--- a/Inventory/Inventory-Master (1).xlsx
+++ b/Inventory/Inventory-Master (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="170">
   <si>
     <t>Item</t>
   </si>
@@ -470,7 +470,58 @@
     <t xml:space="preserve">Cyberpunk Red </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>W'adrhun Hunting Pack-Conquest Regiment Expansion Pack</t>
+  </si>
+  <si>
+    <t>The Count Of Monte Cristo Expansion-Gascony's Legacy</t>
+  </si>
+  <si>
+    <t>The Man in the Iron Mask Expansion-Gascony's Legacy</t>
+  </si>
+  <si>
+    <t>Traveler: Central Supply Catalouge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traveler Deepnight Revelation Rifts Edge Transit </t>
+  </si>
+  <si>
+    <t>Immersive Battle Maps Book-Space-Yarro Studios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comes with sticker pack </t>
+  </si>
+  <si>
+    <t>Bunco Party Board Game</t>
+  </si>
+  <si>
+    <t>New-Celowrap torn</t>
+  </si>
+  <si>
+    <t>Gascony's Legacy Board Game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paranoia  </t>
+  </si>
+  <si>
+    <t>Trek 12 Himilaya</t>
+  </si>
+  <si>
+    <t>Hellboy The Board Game</t>
+  </si>
+  <si>
+    <t>The Seals Of Cthulu</t>
+  </si>
+  <si>
+    <t>Cartographers:Hero's</t>
+  </si>
+  <si>
+    <t>Warhammer Underworlds; 2 player starter set</t>
+  </si>
+  <si>
+    <t>Cthulhu Flux</t>
+  </si>
+  <si>
+    <t>Death On The Cards Agatha Cristhie</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1300,7 @@
         <v>38</v>
       </c>
       <c r="I36" s="1">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="37">
@@ -1543,7 +1594,7 @@
         <v>57</v>
       </c>
       <c r="I57" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="58">
@@ -1851,7 +1902,7 @@
         <v>57</v>
       </c>
       <c r="I79" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="80">
@@ -1879,7 +1930,7 @@
         <v>57</v>
       </c>
       <c r="I81" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="82">
@@ -1893,7 +1944,7 @@
         <v>57</v>
       </c>
       <c r="I82" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="83">
@@ -1907,7 +1958,7 @@
         <v>57</v>
       </c>
       <c r="I83" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="84">
@@ -1921,7 +1972,7 @@
         <v>57</v>
       </c>
       <c r="I84" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="85">
@@ -1935,7 +1986,7 @@
         <v>57</v>
       </c>
       <c r="I85" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="86">
@@ -1963,7 +2014,7 @@
         <v>57</v>
       </c>
       <c r="I87" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="88">
@@ -1977,7 +2028,7 @@
         <v>57</v>
       </c>
       <c r="I88" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="89">
@@ -2117,7 +2168,7 @@
         <v>57</v>
       </c>
       <c r="I98" s="1">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="99">
@@ -2138,10 +2189,241 @@
       <c r="A100" s="1" t="s">
         <v>151</v>
       </c>
+      <c r="C100" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I100" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I102" s="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H104" s="1" t="s">
-        <v>152</v>
+        <v>57</v>
+      </c>
+      <c r="I104" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I105" s="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I106" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I107" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I108" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I109" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I110" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I111" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I112" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I113" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I115" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I116" s="1">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
